--- a/public/templates/klaim/nomor_klaim_reupload.xlsx
+++ b/public/templates/klaim/nomor_klaim_reupload.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\loginusa\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{FE65013F-7519-49CA-96A7-0E5846213070}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B05088B8-1D13-4C6D-9E62-78745CC8A7E0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11760" xr2:uid="{1894F83C-CC08-42FF-8FA0-FD17FB4497EC}"/>
+    <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="16440" xr2:uid="{1894F83C-CC08-42FF-8FA0-FD17FB4497EC}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -34,138 +34,9 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="45" uniqueCount="45">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2" uniqueCount="2">
   <si>
     <t>2026/PROP/SEP/1000718/1000718/138404</t>
-  </si>
-  <si>
-    <t>2026/PROP/SEP/1000718/1000718/138608</t>
-  </si>
-  <si>
-    <t>2026/PROP/SEP/1000718/1000718/138610</t>
-  </si>
-  <si>
-    <t>2026/PROP/SEP/1000718/1000718/138600</t>
-  </si>
-  <si>
-    <t>2026/PROP/SEP/1000718/1000718/138611</t>
-  </si>
-  <si>
-    <t>2026/PROP/SEP/1000718/1000718/138701</t>
-  </si>
-  <si>
-    <t>2026/PROP/SEP/1000718/1000718/138388</t>
-  </si>
-  <si>
-    <t>2026/PROP/SEP/1000718/1000718/138394</t>
-  </si>
-  <si>
-    <t>2026/PROP/SEP/1000718/1000718/138554</t>
-  </si>
-  <si>
-    <t>2026/PROP/SEP/1000718/1000718/138399</t>
-  </si>
-  <si>
-    <t>2026/PROP/SEP/1000718/1000718/137218</t>
-  </si>
-  <si>
-    <t>2026/PROP/SEP/1000718/1000718/137094</t>
-  </si>
-  <si>
-    <t>2026/PROP/SEP/1000718/1000718/137221</t>
-  </si>
-  <si>
-    <t>2026/PROP/SEP/1000718/1000718/137217</t>
-  </si>
-  <si>
-    <t>2026/PROP/SEP/1000718/1000718/137021</t>
-  </si>
-  <si>
-    <t>2026/PROP/SEP/1000718/1000718/136834</t>
-  </si>
-  <si>
-    <t>2026/PROP/SEP/1000718/1000718/137252</t>
-  </si>
-  <si>
-    <t>2026/PROP/SEP/1000718/1000718/137203</t>
-  </si>
-  <si>
-    <t>2026/PROP/SEP/1000718/1000718/136882</t>
-  </si>
-  <si>
-    <t>2026/PROP/SEP/1000718/1000718/137245</t>
-  </si>
-  <si>
-    <t>2026/PROP/SEP/1000718/1000718/137082</t>
-  </si>
-  <si>
-    <t>2026/PROP/SEP/1000718/1000718/137063</t>
-  </si>
-  <si>
-    <t>2026/PROP/SEP/1000718/1000718/137613</t>
-  </si>
-  <si>
-    <t>2026/PROP/SEP/1000718/1000718/138617</t>
-  </si>
-  <si>
-    <t>2026/PROP/SEP/1000718/1000718/138700</t>
-  </si>
-  <si>
-    <t>2026/PROP/SEP/1000718/1000718/137913</t>
-  </si>
-  <si>
-    <t>2026/PROP/SEP/1000718/1000718/138121</t>
-  </si>
-  <si>
-    <t>2026/PROP/SEP/1000718/1000718/138556</t>
-  </si>
-  <si>
-    <t>2026/PROP/SEP/1000718/1000718/138414</t>
-  </si>
-  <si>
-    <t>2026/PROP/SEP/1000718/1000718/138109</t>
-  </si>
-  <si>
-    <t>2026/PROP/SEP/1000718/1000718/137956</t>
-  </si>
-  <si>
-    <t>2026/PROP/SEP/1000718/1000718/138125</t>
-  </si>
-  <si>
-    <t>2026/PROP/SEP/1000718/1000718/138107</t>
-  </si>
-  <si>
-    <t>2026/PROP/SEP/1000718/1000718/137887</t>
-  </si>
-  <si>
-    <t>2026/PROP/SEP/1000718/1000718/138110</t>
-  </si>
-  <si>
-    <t>2026/PROP/SEP/1000718/1000718/138103</t>
-  </si>
-  <si>
-    <t>2026/PROP/SEP/1000718/1000718/138106</t>
-  </si>
-  <si>
-    <t>2026/PROP/SEP/1000718/1000718/137845</t>
-  </si>
-  <si>
-    <t>2026/PROP/SEP/1000718/1000718/137842</t>
-  </si>
-  <si>
-    <t>2026/PROP/SEP/1000718/1000718/137865</t>
-  </si>
-  <si>
-    <t>2026/PROP/SEP/1000718/1000718/137861</t>
-  </si>
-  <si>
-    <t>2026/PROP/SEP/1000718/1000718/137964</t>
-  </si>
-  <si>
-    <t>2026/PROP/SEP/1000718/1000718/136893</t>
-  </si>
-  <si>
-    <t>2026/PROP/SEP/1000718/1000718/138108</t>
   </si>
   <si>
     <t>Nomor Klaim</t>
@@ -528,7 +399,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8654D446-9564-430A-9CA6-276C40CD041B}">
-  <dimension ref="A1:A45"/>
+  <dimension ref="A1:A2"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="38.28515625" bestFit="1" customWidth="1"/>
@@ -536,7 +407,7 @@
   <sheetData>
     <row r="1" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>44</v>
+        <v>1</v>
       </c>
     </row>
     <row r="2" spans="1:1" x14ac:dyDescent="0.25">
@@ -544,221 +415,6 @@
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A3" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="4" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A4" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="5" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A5" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="6" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A6" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="7" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A7" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="8" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A8" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="9" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A9" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="10" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A10" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="11" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A11" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="12" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A12" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="13" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A13" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="14" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A14" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="15" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A15" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="16" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A16" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="17" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A17" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="18" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A18" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="19" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A19" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="20" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A20" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="21" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A21" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="22" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A22" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="23" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A23" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="24" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A24" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="25" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A25" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="26" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A26" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="27" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A27" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="28" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A28" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="29" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A29" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="30" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A30" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="31" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A31" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="32" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A32" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="33" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A33" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="34" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A34" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="35" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A35" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="36" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A36" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="37" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A37" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="38" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A38" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="39" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A39" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="40" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A40" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="41" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A41" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="42" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A42" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="43" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A43" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="44" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A44" t="s">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="45" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A45" t="s">
-        <v>43</v>
-      </c>
-    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
